--- a/pfmea_spinal_peek_cage.xlsx
+++ b/pfmea_spinal_peek_cage.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1. Scope &amp; Planning" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. Structure Analysis" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. Function Analysis" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. Failure Analysis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. Risk Rating" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. Optimization" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. Results Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Scope &amp; Planning" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Structure Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Function Analysis" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Failure Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Risk Rating" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Optimization" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Results Summary" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,12 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -133,6 +139,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
@@ -144,11 +155,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0092D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -183,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -215,49 +221,52 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,7 +278,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -647,7 +656,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 1 – Scope &amp; Planning  |  Injection Molding – PEEK Lumbar Interbody Fusion Cage</t>
+          <t>STEP 1 - Scope &amp; Planning  |  Injection Molding - PEEK Lumbar Interbody Fusion Cage</t>
         </is>
       </c>
     </row>
@@ -673,7 +682,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Injection Molding – PEEK Lumbar Interbody Fusion Cage</t>
+          <t>Injection Molding - PEEK Lumbar Interbody Fusion Cage</t>
         </is>
       </c>
     </row>
@@ -709,7 +718,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Class II – 510(k) (21 CFR 888.3070)</t>
+          <t>Class II - 510(k) (21 CFR 888.3070)</t>
         </is>
       </c>
     </row>
@@ -745,7 +754,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PEEK Lumbar Interbody Fusion Cage – Spinal Implant</t>
+          <t>PEEK Lumbar Interbody Fusion Cage - Spinal Implant</t>
         </is>
       </c>
     </row>
@@ -769,7 +778,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>[Your Name] – Manufacturing Transfer Project Engineer</t>
+          <t>[Your Name] - Quality Engineer</t>
         </is>
       </c>
     </row>
@@ -805,7 +814,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -829,7 +838,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Draft – Internal Review</t>
+          <t>Draft - Internal Review</t>
         </is>
       </c>
     </row>
@@ -880,7 +889,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 2 – Structure Analysis  |  System Hierarchy Breakdown</t>
+          <t>STEP 2 - Structure Analysis  |  System Hierarchy Breakdown</t>
         </is>
       </c>
     </row>
@@ -904,7 +913,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Level 1 – System</t>
+          <t>Level 1 - System</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -921,7 +930,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Level 2 – Subsystem</t>
+          <t>Level 2 - Subsystem</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -938,7 +947,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -955,7 +964,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -972,7 +981,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -989,7 +998,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -1006,7 +1015,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Level 3 – Component</t>
+          <t>Level 3 - Component</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1023,7 +1032,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Level 4 – Interface</t>
+          <t>Level 4 - Interface</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -1040,7 +1049,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Level 4 – Interface</t>
+          <t>Level 4 - Interface</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1088,7 +1097,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 3 – Function Analysis  |  Intended Functions &amp; Requirements</t>
+          <t>STEP 3 - Function Analysis  |  Intended Functions &amp; Requirements</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1233,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>21 CFR 820.184 Device History Record; ISO 13485 section 7.5.3 traceability</t>
+          <t>21 CFR 820.184 Device History Record; ISO 13485 7.5.3 traceability</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1275,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 4 – Failure Analysis  |  Failure Modes, Effects &amp; Causes</t>
+          <t>STEP 4 - Failure Analysis  |  Failure Modes, Effects &amp; Causes</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1319,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Injection Molding – Parting Line</t>
+          <t>Injection Molding - Parting Line</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1345,7 +1354,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Injection Molding – Geometry</t>
+          <t>Injection Molding - Geometry</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -1355,7 +1364,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Implant-endplate mismatch; subsidence risk; non-union – patient harm</t>
+          <t>Implant-endplate mismatch; subsidence risk; non-union - patient harm</t>
         </is>
       </c>
       <c r="D4" s="10" t="n">
@@ -1393,7 +1402,7 @@
           <t>Incorrect mechanical properties; implant fracture or fatigue failure in vivo</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <v>9</v>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1408,14 +1417,14 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Visual label check only – no barcode/CoA lock (DETECTION GAP)</t>
+          <t>Visual label check only - no barcode/CoA lock (DETECTION GAP)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Injection Molding – Fill</t>
+          <t>Injection Molding - Fill</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -1428,7 +1437,7 @@
           <t>Structural porosity in load-bearing cage; fracture risk under spinal loading</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <v>7</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -1443,7 +1452,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Visual inspection – porosity may be subsurface and missed (GAP)</t>
+          <t>Visual inspection - porosity may be subsurface and missed (GAP)</t>
         </is>
       </c>
     </row>
@@ -1463,7 +1472,7 @@
           <t>Mechanical interference with endplate; surgeon re-work; particulate generation</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="10" t="n">
         <v>7</v>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1485,7 +1494,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Injection Molding – Surface</t>
+          <t>Injection Molding - Surface</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -1513,7 +1522,7 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Profilometer sample check per lot – not 100% (DETECTION GAP)</t>
+          <t>Profilometer sample check per lot - not 100% (DETECTION GAP)</t>
         </is>
       </c>
     </row>
@@ -1544,32 +1553,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  AIAG-VDA 2019 Action Priority (AP) -- NOT Traditional RPN</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>AIAG-VDA 2019 replaces RPN (S x O x D) with Action Priority (AP: High / Medium / Low). For spinal implants, an undetected material substitution (wrong PEEK grade) reaching a patient represents a catastrophic fracture risk regardless of how rarely it occurs. AP weights Detection gaps heavily — a D=7 with any S&gt;=9 is automatically High priority.</t>
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>AIAG-VDA 2019 Action Priority (AP) -- NOT Traditional RPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>AIAG-VDA 2019 replaces RPN (SxOxD) with Action Priority (AP: High / Medium / Low). For spinal implants, an undetected material substitution (wrong PEEK grade) reaching a patient represents a catastrophic fracture risk regardless of how rarely it occurs. AP weights Detection gaps heavily - a D=7 with any S&gt;=9 is automatically High priority.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>AP Lookup: S9-10+D7-10-&gt;H | S9-10+D4-6+O&gt;=4-&gt;H | S7-8+D7-10+O&gt;=4-&gt;H | All others-&gt;M or L</t>
         </is>
@@ -1579,7 +1588,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>STEP 5 – Risk Rating  |  AIAG-VDA Action Priority Table</t>
+          <t>STEP 5 - Risk Rating  |  AIAG-VDA Action Priority Table</t>
         </is>
       </c>
     </row>
@@ -1591,19 +1600,19 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>S  (Severity
+          <t>S (Severity
 1-10)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>O  (Occurrence
+          <t>O (Occurrence
 1-10)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D  (Detection
+          <t>D (Detection
 1-10)</t>
         </is>
       </c>
@@ -1631,16 +1640,16 @@
           <t>Flash / fin at parting line</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1650,7 +1659,7 @@
           <t>Lower severity with adequate controls</t>
         </is>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>72</v>
       </c>
     </row>
@@ -1660,16 +1669,16 @@
           <t>Outer footprint or height OOS</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -1679,7 +1688,7 @@
           <t>S=7-8 + D=4-6 + O&gt;=4: moderate risk profile</t>
         </is>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>160</v>
       </c>
     </row>
@@ -1689,26 +1698,26 @@
           <t>Wrong PEEK grade loaded</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>S&gt;=9 + D&gt;=7: undetected critical failure – patient risk</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="n">
+          <t>S&gt;=9 + D&gt;=7: undetected critical failure - patient risk</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="n">
         <v>189</v>
       </c>
     </row>
@@ -1718,16 +1727,16 @@
           <t>Short shot / incomplete fill</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1737,7 +1746,7 @@
           <t>S=7-8 + D&lt;=3: detection adequate for severity level</t>
         </is>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <v>42</v>
       </c>
     </row>
@@ -1747,16 +1756,16 @@
           <t>Gate vestige height &gt; 0.3 mm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -1766,7 +1775,7 @@
           <t>S=7-8 + D=4-6 + O&gt;=4: moderate risk profile</t>
         </is>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <v>112</v>
       </c>
     </row>
@@ -1776,16 +1785,16 @@
           <t>Endplate surface texture OOS</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>H</t>
         </is>
@@ -1795,7 +1804,7 @@
           <t>S=7-8 + D&gt;=7 + O&gt;=4: high-severity, frequent, poorly detected</t>
         </is>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="20" t="n">
         <v>280</v>
       </c>
     </row>
@@ -1831,7 +1840,7 @@
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1842,7 +1851,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 6 – Optimization / Corrective Actions  |  Risk Reduction Plan</t>
+          <t>STEP 6 - Optimization / Corrective Actions  |  Risk Reduction Plan</t>
         </is>
       </c>
     </row>
@@ -1896,8 +1905,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="70" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+    <row r="3" ht="75" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>H</t>
         </is>
@@ -1914,7 +1923,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>MFG PE + Quality</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -1922,23 +1931,23 @@
           <t>2026-Q3</t>
         </is>
       </c>
-      <c r="F3" s="22" t="n">
+      <c r="F3" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="G3" s="22" t="n">
+      <c r="G3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="22" t="n">
+      <c r="H3" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="23" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="70" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+    <row r="4" ht="75" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>H</t>
         </is>
@@ -1963,23 +1972,23 @@
           <t>2026-Q3</t>
         </is>
       </c>
-      <c r="F4" s="24" t="n">
+      <c r="F4" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="24" t="n">
+      <c r="G4" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="24" t="n">
+      <c r="H4" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+    <row r="5" ht="75" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -2004,23 +2013,23 @@
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
+    <row r="6" ht="75" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -2037,7 +2046,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Quality + Mold Eng</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -2045,16 +2054,16 @@
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="24" t="n">
+      <c r="H6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -2095,14 +2104,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STEP 7 – Results &amp; Documentation Summary</t>
+          <t>STEP 7 - Results &amp; Documentation Summary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>pFMEA Metrics Summary</t>
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>pFMEA Metrics Summary (auto-computed)</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2121,7 @@
           <t>Total Failure Modes Analyzed</t>
         </is>
       </c>
-      <c r="D3" s="27" t="n">
+      <c r="D3" s="28" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2122,7 +2131,7 @@
           <t>Initial High (H) Action Priority</t>
         </is>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2132,38 +2141,38 @@
           <t>High AP After Actions Implemented</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Medium (M) AP – Initial</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="n">
+          <t>Medium (M) AP - Initial</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Medium (M) AP – After Actions</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>2</v>
+          <t>Medium (M) AP - After Actions</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Low (L) AP – After Actions</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>4</v>
+          <t>Low (L) AP - After Actions</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2172,7 +2181,7 @@
           <t>Total Corrective Actions Assigned</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="28" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2182,7 +2191,7 @@
           <t>Actions with Owner Assigned</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="29" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2192,13 +2201,13 @@
           <t>Actions with Target Date</t>
         </is>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="28" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Linked Quality System Documents</t>
         </is>
@@ -2239,7 +2248,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Injection Molding – PEEK Spinal Cage Control Plan</t>
+          <t>Injection Molding - PEEK Spinal Cage Control Plan</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -2261,7 +2270,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Injection Molding Setup &amp; Operation – PEEK Cage</t>
+          <t>Injection Molding Setup &amp; Operation - PEEK Cage</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -2283,7 +2292,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>CMM &amp; Vision Inspection – Lumbar Interbody Cage</t>
+          <t>CMM &amp; Vision Inspection - Lumbar Interbody Cage</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -2305,7 +2314,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Injection Press Qualification – PEEK Processing Parameters</t>
+          <t>Injection Press Qualification - PEEK Processing Parameters</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -2327,7 +2336,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Process Validation – PEEK Cage Injection Molding Transfer</t>
+          <t>Process Validation - PEEK Cage Injection Molding Transfer</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -2349,7 +2358,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Device Risk Management File (ISO 14971) – Fusion Cage</t>
+          <t>Device Risk Management File (ISO 14971) - Fusion Cage</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -2371,7 +2380,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Design FMEA – PEEK Lumbar Interbody Fusion Cage</t>
+          <t>Design FMEA - PEEK Lumbar Interbody Fusion Cage</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2404,7 +2413,7 @@
     </row>
     <row r="23"/>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>Archive Location:  [PLM System] -&gt; Projects -&gt; SPINE-CAGE-TRANSFER-2024 -&gt; FMEA -&gt; PFMEA-SPINE-001_RevA.xlsx</t>
         </is>
